--- a/database/event/5495/event_5495_evp_summary.xlsx
+++ b/database/event/5495/event_5495_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.6753</v>
       </c>
       <c r="D2" t="n">
-        <v>2.992</v>
+        <v>2.9223</v>
       </c>
       <c r="E2" t="n">
         <v>8.449299999999999</v>
@@ -548,7 +548,7 @@
         <v>1.5612</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7595</v>
+        <v>2.6931</v>
       </c>
       <c r="E3" t="n">
         <v>7.8739</v>
@@ -594,7 +594,7 @@
         <v>1.3561</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3418</v>
+        <v>2.2811</v>
       </c>
       <c r="E4" t="n">
         <v>6.8398</v>
@@ -640,7 +640,7 @@
         <v>1.2815</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E5" t="n">
         <v>6.4635</v>
@@ -686,7 +686,7 @@
         <v>1.2815</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E6" t="n">
         <v>6.4635</v>
@@ -732,7 +732,7 @@
         <v>1.1508</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9234</v>
+        <v>1.8685</v>
       </c>
       <c r="E7" t="n">
         <v>5.8043</v>
@@ -778,7 +778,7 @@
         <v>1.1263</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8734</v>
+        <v>1.8192</v>
       </c>
       <c r="E8" t="n">
         <v>5.6804</v>
@@ -824,7 +824,7 @@
         <v>1.0042</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6248</v>
+        <v>1.574</v>
       </c>
       <c r="E9" t="n">
         <v>5.065</v>
@@ -870,7 +870,7 @@
         <v>0.9649</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5446</v>
+        <v>1.4949</v>
       </c>
       <c r="E10" t="n">
         <v>4.8665</v>
@@ -916,7 +916,7 @@
         <v>0.9625</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5398</v>
+        <v>1.4902</v>
       </c>
       <c r="E11" t="n">
         <v>4.8547</v>
@@ -962,7 +962,7 @@
         <v>0.9191</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4514</v>
+        <v>1.403</v>
       </c>
       <c r="E12" t="n">
         <v>4.6358</v>
@@ -1008,7 +1008,7 @@
         <v>0.8764999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3645</v>
+        <v>1.3173</v>
       </c>
       <c r="E13" t="n">
         <v>4.4208</v>
@@ -1054,7 +1054,7 @@
         <v>0.7995</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2076</v>
+        <v>1.1625</v>
       </c>
       <c r="E14" t="n">
         <v>4.0322</v>
@@ -1100,7 +1100,7 @@
         <v>0.7746</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1569</v>
+        <v>1.1126</v>
       </c>
       <c r="E15" t="n">
         <v>3.9068</v>
@@ -1146,7 +1146,7 @@
         <v>0.7496</v>
       </c>
       <c r="D16" t="n">
-        <v>1.106</v>
+        <v>1.0624</v>
       </c>
       <c r="E16" t="n">
         <v>3.7808</v>
@@ -1192,7 +1192,7 @@
         <v>0.6941000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9928</v>
+        <v>0.9507</v>
       </c>
       <c r="E17" t="n">
         <v>3.5006</v>
@@ -1238,7 +1238,7 @@
         <v>0.6922</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9891</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="E18" t="n">
         <v>3.4914</v>
@@ -1284,7 +1284,7 @@
         <v>0.6192</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8403</v>
+        <v>0.8003</v>
       </c>
       <c r="E19" t="n">
         <v>3.123</v>
@@ -1330,7 +1330,7 @@
         <v>0.6131</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8278</v>
+        <v>0.788</v>
       </c>
       <c r="E20" t="n">
         <v>3.0921</v>
@@ -1376,7 +1376,7 @@
         <v>0.6027</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8066</v>
+        <v>0.7671</v>
       </c>
       <c r="E21" t="n">
         <v>3.0398</v>
@@ -1422,7 +1422,7 @@
         <v>0.5903</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7814</v>
+        <v>0.7423</v>
       </c>
       <c r="E22" t="n">
         <v>2.9774</v>
@@ -1468,7 +1468,7 @@
         <v>0.5676</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7351</v>
+        <v>0.6965</v>
       </c>
       <c r="E23" t="n">
         <v>2.8626</v>
@@ -1514,7 +1514,7 @@
         <v>0.4992</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5958</v>
+        <v>0.5592</v>
       </c>
       <c r="E24" t="n">
         <v>2.5179</v>
@@ -1560,7 +1560,7 @@
         <v>0.4751</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5467</v>
+        <v>0.5108</v>
       </c>
       <c r="E25" t="n">
         <v>2.3963</v>
@@ -1606,7 +1606,7 @@
         <v>0.3484</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2885</v>
+        <v>0.2562</v>
       </c>
       <c r="E26" t="n">
         <v>1.7573</v>
@@ -1652,7 +1652,7 @@
         <v>0.3101</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2105</v>
+        <v>0.1793</v>
       </c>
       <c r="E27" t="n">
         <v>1.5642</v>
@@ -1698,7 +1698,7 @@
         <v>0.2719</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1325</v>
+        <v>0.1023</v>
       </c>
       <c r="E28" t="n">
         <v>1.3711</v>
@@ -1744,7 +1744,7 @@
         <v>0.1931</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0279</v>
+        <v>-0.0559</v>
       </c>
       <c r="E29" t="n">
         <v>0.974</v>
@@ -1790,7 +1790,7 @@
         <v>0.1597</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.096</v>
+        <v>-0.123</v>
       </c>
       <c r="E30" t="n">
         <v>0.8055</v>
@@ -1836,7 +1836,7 @@
         <v>0.1018</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.214</v>
+        <v>-0.2394</v>
       </c>
       <c r="E31" t="n">
         <v>0.5133</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0599</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5434</v>
+        <v>-0.5643</v>
       </c>
       <c r="E32" t="n">
         <v>-0.3022</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0659</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5556</v>
+        <v>-0.5763</v>
       </c>
       <c r="E33" t="n">
         <v>-0.3323</v>
@@ -1974,7 +1974,7 @@
         <v>-0.08550000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5955</v>
+        <v>-0.6157</v>
       </c>
       <c r="E34" t="n">
         <v>-0.4311</v>
@@ -2020,7 +2020,7 @@
         <v>-0.131</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.6883</v>
+        <v>-0.7071</v>
       </c>
       <c r="E35" t="n">
         <v>-0.6607</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1621</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7517</v>
+        <v>-0.7696</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8176</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1882</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8048</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="E37" t="n">
         <v>-0.9492</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2821</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9961</v>
+        <v>-1.0108</v>
       </c>
       <c r="E38" t="n">
         <v>-1.4228</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4385</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3148</v>
+        <v>-1.325</v>
       </c>
       <c r="E39" t="n">
         <v>-2.2116</v>
@@ -2250,7 +2250,7 @@
         <v>-0.5099</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4602</v>
+        <v>-1.4684</v>
       </c>
       <c r="E40" t="n">
         <v>-2.5716</v>
@@ -2296,7 +2296,7 @@
         <v>-0.5714</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5855</v>
+        <v>-1.592</v>
       </c>
       <c r="E41" t="n">
         <v>-2.8817</v>
@@ -2342,7 +2342,7 @@
         <v>-0.7408</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.9307</v>
+        <v>-1.9324</v>
       </c>
       <c r="E42" t="n">
         <v>-3.7362</v>
